--- a/data.xlsx
+++ b/data.xlsx
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CMTHANG\playwright-everything-main\playwright-everything-main\playwright-python\session_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qlnha\Desktop\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A41FCC-CC0D-44E8-B347-B00A567373A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64088383-A1DC-4B0A-96E7-3ED07800A9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="429" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="429" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="CanHo" sheetId="3" r:id="rId3"/>
     <sheet name="GIAM" sheetId="4" r:id="rId4"/>
-    <sheet name="Project" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="BaoCao" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Project" sheetId="5" r:id="rId5"/>
+    <sheet name="BaoCao" sheetId="6" r:id="rId6"/>
     <sheet name="NoCu" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet name="DaThanhToan" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CanHo!$A$1:$R$176</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$1:$C$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$1:$C$201</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="603">
   <si>
     <t>email</t>
   </si>
@@ -589,1401 +589,6 @@
     <t>A2-05</t>
   </si>
   <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>1228</t>
-  </si>
-  <si>
-    <t>1316</t>
-  </si>
-  <si>
-    <t>1329</t>
-  </si>
-  <si>
-    <t>1330</t>
-  </si>
-  <si>
-    <t>1334</t>
-  </si>
-  <si>
-    <t>1508</t>
-  </si>
-  <si>
-    <t>1528</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>0413</t>
-  </si>
-  <si>
-    <t>0427</t>
-  </si>
-  <si>
-    <t>0434</t>
-  </si>
-  <si>
-    <t>0531</t>
-  </si>
-  <si>
-    <t>0626</t>
-  </si>
-  <si>
-    <t>0630</t>
-  </si>
-  <si>
-    <t>0813</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>1030</t>
-  </si>
-  <si>
-    <t>1031</t>
-  </si>
-  <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>1133</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>1207</t>
-  </si>
-  <si>
-    <t>1209</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>1211</t>
-  </si>
-  <si>
-    <t>1212</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
-    <t>1214</t>
-  </si>
-  <si>
-    <t>1215</t>
-  </si>
-  <si>
-    <t>1217</t>
-  </si>
-  <si>
-    <t>1218</t>
-  </si>
-  <si>
-    <t>1219</t>
-  </si>
-  <si>
-    <t>1220</t>
-  </si>
-  <si>
-    <t>1221</t>
-  </si>
-  <si>
-    <t>1222</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>1224</t>
-  </si>
-  <si>
-    <t>1225</t>
-  </si>
-  <si>
-    <t>1227</t>
-  </si>
-  <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>1235</t>
-  </si>
-  <si>
-    <t>1302</t>
-  </si>
-  <si>
-    <t>1303</t>
-  </si>
-  <si>
-    <t>1304</t>
-  </si>
-  <si>
-    <t>1305</t>
-  </si>
-  <si>
-    <t>1306</t>
-  </si>
-  <si>
-    <t>1307</t>
-  </si>
-  <si>
-    <t>1308</t>
-  </si>
-  <si>
-    <t>1309</t>
-  </si>
-  <si>
-    <t>1310</t>
-  </si>
-  <si>
-    <t>1311</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>1230</t>
-  </si>
-  <si>
-    <t>1231</t>
-  </si>
-  <si>
-    <t>1312</t>
-  </si>
-  <si>
-    <t>1313</t>
-  </si>
-  <si>
-    <t>1314</t>
-  </si>
-  <si>
-    <t>1317</t>
-  </si>
-  <si>
-    <t>1320</t>
-  </si>
-  <si>
-    <t>1321</t>
-  </si>
-  <si>
-    <t>1322</t>
-  </si>
-  <si>
-    <t>1323</t>
-  </si>
-  <si>
-    <t>1324</t>
-  </si>
-  <si>
-    <t>1325</t>
-  </si>
-  <si>
-    <t>1326</t>
-  </si>
-  <si>
-    <t>1327</t>
-  </si>
-  <si>
-    <t>1328</t>
-  </si>
-  <si>
-    <t>1331</t>
-  </si>
-  <si>
-    <t>1332</t>
-  </si>
-  <si>
-    <t>1333</t>
-  </si>
-  <si>
-    <t>1335</t>
-  </si>
-  <si>
-    <t>1401</t>
-  </si>
-  <si>
-    <t>1402</t>
-  </si>
-  <si>
-    <t>1403</t>
-  </si>
-  <si>
-    <t>1404</t>
-  </si>
-  <si>
-    <t>1406</t>
-  </si>
-  <si>
-    <t>1407</t>
-  </si>
-  <si>
-    <t>1408</t>
-  </si>
-  <si>
-    <t>1409</t>
-  </si>
-  <si>
-    <t>1410</t>
-  </si>
-  <si>
-    <t>1412</t>
-  </si>
-  <si>
-    <t>1413</t>
-  </si>
-  <si>
-    <t>1414</t>
-  </si>
-  <si>
-    <t>1415</t>
-  </si>
-  <si>
-    <t>1416</t>
-  </si>
-  <si>
-    <t>1417</t>
-  </si>
-  <si>
-    <t>1418</t>
-  </si>
-  <si>
-    <t>1420</t>
-  </si>
-  <si>
-    <t>1421</t>
-  </si>
-  <si>
-    <t>1423</t>
-  </si>
-  <si>
-    <t>1425</t>
-  </si>
-  <si>
-    <t>1426</t>
-  </si>
-  <si>
-    <t>1427</t>
-  </si>
-  <si>
-    <t>1428</t>
-  </si>
-  <si>
-    <t>1429</t>
-  </si>
-  <si>
-    <t>1430</t>
-  </si>
-  <si>
-    <t>1431</t>
-  </si>
-  <si>
-    <t>1432</t>
-  </si>
-  <si>
-    <t>1433</t>
-  </si>
-  <si>
-    <t>1435</t>
-  </si>
-  <si>
-    <t>1502</t>
-  </si>
-  <si>
-    <t>1503</t>
-  </si>
-  <si>
-    <t>1504</t>
-  </si>
-  <si>
-    <t>1505</t>
-  </si>
-  <si>
-    <t>1506</t>
-  </si>
-  <si>
-    <t>1507</t>
-  </si>
-  <si>
-    <t>1509</t>
-  </si>
-  <si>
-    <t>1510</t>
-  </si>
-  <si>
-    <t>1511</t>
-  </si>
-  <si>
-    <t>1512</t>
-  </si>
-  <si>
-    <t>1513</t>
-  </si>
-  <si>
-    <t>1514</t>
-  </si>
-  <si>
-    <t>1515</t>
-  </si>
-  <si>
-    <t>1516</t>
-  </si>
-  <si>
-    <t>1517</t>
-  </si>
-  <si>
-    <t>1519</t>
-  </si>
-  <si>
-    <t>1520</t>
-  </si>
-  <si>
-    <t>1521</t>
-  </si>
-  <si>
-    <t>1522</t>
-  </si>
-  <si>
-    <t>1523</t>
-  </si>
-  <si>
-    <t>1524</t>
-  </si>
-  <si>
-    <t>1525</t>
-  </si>
-  <si>
-    <t>1526</t>
-  </si>
-  <si>
-    <t>1527</t>
-  </si>
-  <si>
-    <t>1529</t>
-  </si>
-  <si>
-    <t>1531</t>
-  </si>
-  <si>
-    <t>1532</t>
-  </si>
-  <si>
-    <t>1533</t>
-  </si>
-  <si>
-    <t>1534</t>
-  </si>
-  <si>
-    <t>1535</t>
-  </si>
-  <si>
-    <t>1602</t>
-  </si>
-  <si>
-    <t>1603</t>
-  </si>
-  <si>
-    <t>1604</t>
-  </si>
-  <si>
-    <t>1605</t>
-  </si>
-  <si>
-    <t>1606</t>
-  </si>
-  <si>
-    <t>1607</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1613</t>
-  </si>
-  <si>
-    <t>1615</t>
-  </si>
-  <si>
-    <t>1616</t>
-  </si>
-  <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>1618</t>
-  </si>
-  <si>
-    <t>1619</t>
-  </si>
-  <si>
-    <t>1620</t>
-  </si>
-  <si>
-    <t>1621</t>
-  </si>
-  <si>
-    <t>1622</t>
-  </si>
-  <si>
-    <t>1623</t>
-  </si>
-  <si>
-    <t>1624</t>
-  </si>
-  <si>
-    <t>1626</t>
-  </si>
-  <si>
-    <t>1628</t>
-  </si>
-  <si>
-    <t>1629</t>
-  </si>
-  <si>
-    <t>1631</t>
-  </si>
-  <si>
-    <t>1633</t>
-  </si>
-  <si>
-    <t>1634</t>
-  </si>
-  <si>
-    <t>1635</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1713</t>
-  </si>
-  <si>
-    <t>1714</t>
-  </si>
-  <si>
-    <t>1715</t>
-  </si>
-  <si>
-    <t>1717</t>
-  </si>
-  <si>
-    <t>1718</t>
-  </si>
-  <si>
-    <t>1720</t>
-  </si>
-  <si>
-    <t>1721</t>
-  </si>
-  <si>
-    <t>1722</t>
-  </si>
-  <si>
-    <t>1724</t>
-  </si>
-  <si>
-    <t>1725</t>
-  </si>
-  <si>
-    <t>1726</t>
-  </si>
-  <si>
-    <t>1727</t>
-  </si>
-  <si>
-    <t>1728</t>
-  </si>
-  <si>
-    <t>1729</t>
-  </si>
-  <si>
-    <t>1730</t>
-  </si>
-  <si>
-    <t>1731</t>
-  </si>
-  <si>
-    <t>1732</t>
-  </si>
-  <si>
-    <t>1733</t>
-  </si>
-  <si>
-    <t>1734</t>
-  </si>
-  <si>
-    <t>1735</t>
-  </si>
-  <si>
-    <t>0302</t>
-  </si>
-  <si>
-    <t>0303</t>
-  </si>
-  <si>
-    <t>0304</t>
-  </si>
-  <si>
-    <t>0305</t>
-  </si>
-  <si>
-    <t>0307</t>
-  </si>
-  <si>
-    <t>0308</t>
-  </si>
-  <si>
-    <t>0309</t>
-  </si>
-  <si>
-    <t>0311</t>
-  </si>
-  <si>
-    <t>0312</t>
-  </si>
-  <si>
-    <t>0314</t>
-  </si>
-  <si>
-    <t>0315</t>
-  </si>
-  <si>
-    <t>0316</t>
-  </si>
-  <si>
-    <t>0317</t>
-  </si>
-  <si>
-    <t>0318</t>
-  </si>
-  <si>
-    <t>0319</t>
-  </si>
-  <si>
-    <t>0320</t>
-  </si>
-  <si>
-    <t>0321</t>
-  </si>
-  <si>
-    <t>0402</t>
-  </si>
-  <si>
-    <t>0403</t>
-  </si>
-  <si>
-    <t>0406</t>
-  </si>
-  <si>
-    <t>0407</t>
-  </si>
-  <si>
-    <t>0408</t>
-  </si>
-  <si>
-    <t>0409</t>
-  </si>
-  <si>
-    <t>0410</t>
-  </si>
-  <si>
-    <t>0411</t>
-  </si>
-  <si>
-    <t>0412</t>
-  </si>
-  <si>
-    <t>0414</t>
-  </si>
-  <si>
-    <t>0415</t>
-  </si>
-  <si>
-    <t>0416</t>
-  </si>
-  <si>
-    <t>0418</t>
-  </si>
-  <si>
-    <t>0419</t>
-  </si>
-  <si>
-    <t>0420</t>
-  </si>
-  <si>
-    <t>0421</t>
-  </si>
-  <si>
-    <t>0422</t>
-  </si>
-  <si>
-    <t>0423</t>
-  </si>
-  <si>
-    <t>0425</t>
-  </si>
-  <si>
-    <t>0426</t>
-  </si>
-  <si>
-    <t>0429</t>
-  </si>
-  <si>
-    <t>0430</t>
-  </si>
-  <si>
-    <t>0431</t>
-  </si>
-  <si>
-    <t>0433</t>
-  </si>
-  <si>
-    <t>0435</t>
-  </si>
-  <si>
-    <t>0501</t>
-  </si>
-  <si>
-    <t>0502</t>
-  </si>
-  <si>
-    <t>0504</t>
-  </si>
-  <si>
-    <t>0505</t>
-  </si>
-  <si>
-    <t>0507</t>
-  </si>
-  <si>
-    <t>0509</t>
-  </si>
-  <si>
-    <t>0510</t>
-  </si>
-  <si>
-    <t>0511</t>
-  </si>
-  <si>
-    <t>0512</t>
-  </si>
-  <si>
-    <t>0513</t>
-  </si>
-  <si>
-    <t>0514</t>
-  </si>
-  <si>
-    <t>0516</t>
-  </si>
-  <si>
-    <t>0518</t>
-  </si>
-  <si>
-    <t>0519</t>
-  </si>
-  <si>
-    <t>0521</t>
-  </si>
-  <si>
-    <t>0522</t>
-  </si>
-  <si>
-    <t>0524</t>
-  </si>
-  <si>
-    <t>0526</t>
-  </si>
-  <si>
-    <t>0527</t>
-  </si>
-  <si>
-    <t>0528</t>
-  </si>
-  <si>
-    <t>0529</t>
-  </si>
-  <si>
-    <t>0530</t>
-  </si>
-  <si>
-    <t>0532</t>
-  </si>
-  <si>
-    <t>0533</t>
-  </si>
-  <si>
-    <t>0535</t>
-  </si>
-  <si>
-    <t>0601</t>
-  </si>
-  <si>
-    <t>0603</t>
-  </si>
-  <si>
-    <t>0604</t>
-  </si>
-  <si>
-    <t>0605</t>
-  </si>
-  <si>
-    <t>0606</t>
-  </si>
-  <si>
-    <t>0607</t>
-  </si>
-  <si>
-    <t>0608</t>
-  </si>
-  <si>
-    <t>0609</t>
-  </si>
-  <si>
-    <t>0611</t>
-  </si>
-  <si>
-    <t>0612</t>
-  </si>
-  <si>
-    <t>0613</t>
-  </si>
-  <si>
-    <t>0614</t>
-  </si>
-  <si>
-    <t>0615</t>
-  </si>
-  <si>
-    <t>0616</t>
-  </si>
-  <si>
-    <t>0617</t>
-  </si>
-  <si>
-    <t>0618</t>
-  </si>
-  <si>
-    <t>0620</t>
-  </si>
-  <si>
-    <t>0621</t>
-  </si>
-  <si>
-    <t>0622</t>
-  </si>
-  <si>
-    <t>0623</t>
-  </si>
-  <si>
-    <t>0625</t>
-  </si>
-  <si>
-    <t>0627</t>
-  </si>
-  <si>
-    <t>0628</t>
-  </si>
-  <si>
-    <t>0629</t>
-  </si>
-  <si>
-    <t>0632</t>
-  </si>
-  <si>
-    <t>0633</t>
-  </si>
-  <si>
-    <t>0635</t>
-  </si>
-  <si>
-    <t>0701</t>
-  </si>
-  <si>
-    <t>0703</t>
-  </si>
-  <si>
-    <t>0705</t>
-  </si>
-  <si>
-    <t>0706</t>
-  </si>
-  <si>
-    <t>0708</t>
-  </si>
-  <si>
-    <t>0709</t>
-  </si>
-  <si>
-    <t>0710</t>
-  </si>
-  <si>
-    <t>0711</t>
-  </si>
-  <si>
-    <t>0712</t>
-  </si>
-  <si>
-    <t>0713</t>
-  </si>
-  <si>
-    <t>0715</t>
-  </si>
-  <si>
-    <t>0716</t>
-  </si>
-  <si>
-    <t>0717</t>
-  </si>
-  <si>
-    <t>0718</t>
-  </si>
-  <si>
-    <t>0719</t>
-  </si>
-  <si>
-    <t>0720</t>
-  </si>
-  <si>
-    <t>0721</t>
-  </si>
-  <si>
-    <t>0724</t>
-  </si>
-  <si>
-    <t>0725</t>
-  </si>
-  <si>
-    <t>0726</t>
-  </si>
-  <si>
-    <t>0727</t>
-  </si>
-  <si>
-    <t>0728</t>
-  </si>
-  <si>
-    <t>0729</t>
-  </si>
-  <si>
-    <t>0732</t>
-  </si>
-  <si>
-    <t>0733</t>
-  </si>
-  <si>
-    <t>0801</t>
-  </si>
-  <si>
-    <t>0804</t>
-  </si>
-  <si>
-    <t>0806</t>
-  </si>
-  <si>
-    <t>0807</t>
-  </si>
-  <si>
-    <t>0808</t>
-  </si>
-  <si>
-    <t>0809</t>
-  </si>
-  <si>
-    <t>0810</t>
-  </si>
-  <si>
-    <t>0812</t>
-  </si>
-  <si>
-    <t>0814</t>
-  </si>
-  <si>
-    <t>0815</t>
-  </si>
-  <si>
-    <t>0816</t>
-  </si>
-  <si>
-    <t>0818</t>
-  </si>
-  <si>
-    <t>0819</t>
-  </si>
-  <si>
-    <t>0822</t>
-  </si>
-  <si>
-    <t>0823</t>
-  </si>
-  <si>
-    <t>0824</t>
-  </si>
-  <si>
-    <t>0825</t>
-  </si>
-  <si>
-    <t>0826</t>
-  </si>
-  <si>
-    <t>0831</t>
-  </si>
-  <si>
-    <t>0832</t>
-  </si>
-  <si>
-    <t>0834</t>
-  </si>
-  <si>
-    <t>0835</t>
-  </si>
-  <si>
-    <t>0901</t>
-  </si>
-  <si>
-    <t>0902</t>
-  </si>
-  <si>
-    <t>0906</t>
-  </si>
-  <si>
-    <t>0907</t>
-  </si>
-  <si>
-    <t>0908</t>
-  </si>
-  <si>
-    <t>0909</t>
-  </si>
-  <si>
-    <t>0910</t>
-  </si>
-  <si>
-    <t>0911</t>
-  </si>
-  <si>
-    <t>0912</t>
-  </si>
-  <si>
-    <t>0913</t>
-  </si>
-  <si>
-    <t>0914</t>
-  </si>
-  <si>
-    <t>0915</t>
-  </si>
-  <si>
-    <t>0916</t>
-  </si>
-  <si>
-    <t>0917</t>
-  </si>
-  <si>
-    <t>0918</t>
-  </si>
-  <si>
-    <t>0919</t>
-  </si>
-  <si>
-    <t>0920</t>
-  </si>
-  <si>
-    <t>0921</t>
-  </si>
-  <si>
-    <t>0924</t>
-  </si>
-  <si>
-    <t>0926</t>
-  </si>
-  <si>
-    <t>0927</t>
-  </si>
-  <si>
-    <t>0929</t>
-  </si>
-  <si>
-    <t>0930</t>
-  </si>
-  <si>
-    <t>0931</t>
-  </si>
-  <si>
-    <t>0932</t>
-  </si>
-  <si>
-    <t>0934</t>
-  </si>
-  <si>
-    <t>0935</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>1530</t>
-  </si>
-  <si>
-    <t>1632</t>
-  </si>
-  <si>
-    <t>1716</t>
-  </si>
-  <si>
-    <t>0424</t>
-  </si>
-  <si>
-    <t>0508</t>
-  </si>
-  <si>
-    <t>0517</t>
-  </si>
-  <si>
-    <t>0525</t>
-  </si>
-  <si>
-    <t>0634</t>
-  </si>
-  <si>
-    <t>0827</t>
-  </si>
-  <si>
-    <t>0828</t>
-  </si>
-  <si>
-    <t>0313</t>
-  </si>
-  <si>
-    <t>0401</t>
-  </si>
-  <si>
-    <t>0404</t>
-  </si>
-  <si>
-    <t>0405</t>
-  </si>
-  <si>
-    <t>0417</t>
-  </si>
-  <si>
-    <t>0515</t>
-  </si>
-  <si>
-    <t>0624</t>
-  </si>
-  <si>
-    <t>0631</t>
-  </si>
-  <si>
-    <t>0707</t>
-  </si>
-  <si>
-    <t>0714</t>
-  </si>
-  <si>
-    <t>0722</t>
-  </si>
-  <si>
-    <t>0730</t>
-  </si>
-  <si>
-    <t>0735</t>
-  </si>
-  <si>
-    <t>0802</t>
-  </si>
-  <si>
-    <t>0803</t>
-  </si>
-  <si>
-    <t>0820</t>
-  </si>
-  <si>
-    <t>0830</t>
-  </si>
-  <si>
-    <t>0833</t>
-  </si>
-  <si>
-    <t>0905</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>1034</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>1208</t>
-  </si>
-  <si>
-    <t>1226</t>
-  </si>
-  <si>
-    <t>1315</t>
-  </si>
-  <si>
-    <t>1318</t>
-  </si>
-  <si>
-    <t>1319</t>
-  </si>
-  <si>
-    <t>1419</t>
-  </si>
-  <si>
-    <t>1424</t>
-  </si>
-  <si>
-    <t>1434</t>
-  </si>
-  <si>
-    <t>1501</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1614</t>
-  </si>
-  <si>
-    <t>1627</t>
-  </si>
-  <si>
-    <t>1723</t>
-  </si>
-  <si>
-    <t>12/2025</t>
-  </si>
-  <si>
     <t>B01.01</t>
   </si>
   <si>
@@ -2509,17 +1114,752 @@
     <t>TẦNG.3C</t>
   </si>
   <si>
-    <t>bql.hungphatsilverstar@khaservice.com.vn</t>
-  </si>
-  <si>
-    <t>Bqlhungphat2025@</t>
+    <t>03/2026</t>
+  </si>
+  <si>
+    <t>E.02.01</t>
+  </si>
+  <si>
+    <t>E.02.02</t>
+  </si>
+  <si>
+    <t>E.02.03</t>
+  </si>
+  <si>
+    <t>E.02.04</t>
+  </si>
+  <si>
+    <t>E.02.05</t>
+  </si>
+  <si>
+    <t>E.02.06</t>
+  </si>
+  <si>
+    <t>E.02.07</t>
+  </si>
+  <si>
+    <t>E.02.08</t>
+  </si>
+  <si>
+    <t>E.02.09</t>
+  </si>
+  <si>
+    <t>E.02.10</t>
+  </si>
+  <si>
+    <t>E.03.01</t>
+  </si>
+  <si>
+    <t>E.03.02</t>
+  </si>
+  <si>
+    <t>E.03.03</t>
+  </si>
+  <si>
+    <t>E.03.05</t>
+  </si>
+  <si>
+    <t>E.03.06</t>
+  </si>
+  <si>
+    <t>E.03.07</t>
+  </si>
+  <si>
+    <t>E.03.08</t>
+  </si>
+  <si>
+    <t>E.03.09</t>
+  </si>
+  <si>
+    <t>E.03.10</t>
+  </si>
+  <si>
+    <t>E.04.01</t>
+  </si>
+  <si>
+    <t>E.04.02</t>
+  </si>
+  <si>
+    <t>E.04.03</t>
+  </si>
+  <si>
+    <t>E.04.04</t>
+  </si>
+  <si>
+    <t>E.04.05</t>
+  </si>
+  <si>
+    <t>E.04.06</t>
+  </si>
+  <si>
+    <t>E.04.07</t>
+  </si>
+  <si>
+    <t>E.04.08</t>
+  </si>
+  <si>
+    <t>E.04.09</t>
+  </si>
+  <si>
+    <t>E.04.10</t>
+  </si>
+  <si>
+    <t>E.05.01</t>
+  </si>
+  <si>
+    <t>E.05.02</t>
+  </si>
+  <si>
+    <t>E.05.04</t>
+  </si>
+  <si>
+    <t>E.05.05</t>
+  </si>
+  <si>
+    <t>E.05.06</t>
+  </si>
+  <si>
+    <t>E.05.08</t>
+  </si>
+  <si>
+    <t>E.06.03</t>
+  </si>
+  <si>
+    <t>E.06.04</t>
+  </si>
+  <si>
+    <t>E.06.05</t>
+  </si>
+  <si>
+    <t>E.06.06</t>
+  </si>
+  <si>
+    <t>E.06.07</t>
+  </si>
+  <si>
+    <t>E.06.10</t>
+  </si>
+  <si>
+    <t>E.07.01</t>
+  </si>
+  <si>
+    <t>E.07.02</t>
+  </si>
+  <si>
+    <t>E.07.04</t>
+  </si>
+  <si>
+    <t>E.07.05</t>
+  </si>
+  <si>
+    <t>E.07.06</t>
+  </si>
+  <si>
+    <t>E.07.07</t>
+  </si>
+  <si>
+    <t>E.07.08</t>
+  </si>
+  <si>
+    <t>E.07.09</t>
+  </si>
+  <si>
+    <t>E.07.10</t>
+  </si>
+  <si>
+    <t>E.08.01</t>
+  </si>
+  <si>
+    <t>E.08.03</t>
+  </si>
+  <si>
+    <t>E.08.04</t>
+  </si>
+  <si>
+    <t>E.08.05</t>
+  </si>
+  <si>
+    <t>E.08.06</t>
+  </si>
+  <si>
+    <t>E.08.07</t>
+  </si>
+  <si>
+    <t>E.08.08</t>
+  </si>
+  <si>
+    <t>E.08.09</t>
+  </si>
+  <si>
+    <t>E.08.10</t>
+  </si>
+  <si>
+    <t>E.09.01</t>
+  </si>
+  <si>
+    <t>E.09.02</t>
+  </si>
+  <si>
+    <t>E.09.04</t>
+  </si>
+  <si>
+    <t>E.09.05</t>
+  </si>
+  <si>
+    <t>E.09.06</t>
+  </si>
+  <si>
+    <t>E.09.07</t>
+  </si>
+  <si>
+    <t>E.09.10</t>
+  </si>
+  <si>
+    <t>E.10.01</t>
+  </si>
+  <si>
+    <t>E.10.02</t>
+  </si>
+  <si>
+    <t>E.10.03</t>
+  </si>
+  <si>
+    <t>E.10.04</t>
+  </si>
+  <si>
+    <t>E.10.05</t>
+  </si>
+  <si>
+    <t>E.10.07</t>
+  </si>
+  <si>
+    <t>E.10.08</t>
+  </si>
+  <si>
+    <t>E.10.09</t>
+  </si>
+  <si>
+    <t>E.10.10</t>
+  </si>
+  <si>
+    <t>E.11.01</t>
+  </si>
+  <si>
+    <t>E.11.02</t>
+  </si>
+  <si>
+    <t>E.11.03</t>
+  </si>
+  <si>
+    <t>E.11.04</t>
+  </si>
+  <si>
+    <t>E.11.05</t>
+  </si>
+  <si>
+    <t>E.11.06</t>
+  </si>
+  <si>
+    <t>E.11.07</t>
+  </si>
+  <si>
+    <t>E.11.08</t>
+  </si>
+  <si>
+    <t>E.11.09</t>
+  </si>
+  <si>
+    <t>E.11.10</t>
+  </si>
+  <si>
+    <t>E.12.01</t>
+  </si>
+  <si>
+    <t>E.12.02</t>
+  </si>
+  <si>
+    <t>E.12.03</t>
+  </si>
+  <si>
+    <t>E.12.04</t>
+  </si>
+  <si>
+    <t>E.12.05</t>
+  </si>
+  <si>
+    <t>E.12.06</t>
+  </si>
+  <si>
+    <t>E.12.07</t>
+  </si>
+  <si>
+    <t>E.12.09</t>
+  </si>
+  <si>
+    <t>E.12.10</t>
+  </si>
+  <si>
+    <t>E.14.01</t>
+  </si>
+  <si>
+    <t>E.14.03</t>
+  </si>
+  <si>
+    <t>E.14.04</t>
+  </si>
+  <si>
+    <t>E.14.05</t>
+  </si>
+  <si>
+    <t>E.14.06</t>
+  </si>
+  <si>
+    <t>E.14.07</t>
+  </si>
+  <si>
+    <t>E.14.08</t>
+  </si>
+  <si>
+    <t>E.14.10</t>
+  </si>
+  <si>
+    <t>E.15.01</t>
+  </si>
+  <si>
+    <t>E.15.02</t>
+  </si>
+  <si>
+    <t>E.15.03</t>
+  </si>
+  <si>
+    <t>E.15.04</t>
+  </si>
+  <si>
+    <t>E.15.05</t>
+  </si>
+  <si>
+    <t>E.15.06</t>
+  </si>
+  <si>
+    <t>E.15.07</t>
+  </si>
+  <si>
+    <t>E.15.08</t>
+  </si>
+  <si>
+    <t>E.15.09</t>
+  </si>
+  <si>
+    <t>E.15.10</t>
+  </si>
+  <si>
+    <t>E.16.01</t>
+  </si>
+  <si>
+    <t>E.16.02</t>
+  </si>
+  <si>
+    <t>E.16.03</t>
+  </si>
+  <si>
+    <t>E.16.06</t>
+  </si>
+  <si>
+    <t>E.16.07</t>
+  </si>
+  <si>
+    <t>E.17.01</t>
+  </si>
+  <si>
+    <t>E.17.02</t>
+  </si>
+  <si>
+    <t>E.17.03</t>
+  </si>
+  <si>
+    <t>E.17.04</t>
+  </si>
+  <si>
+    <t>E.17.05</t>
+  </si>
+  <si>
+    <t>E.17.06</t>
+  </si>
+  <si>
+    <t>W.02.01</t>
+  </si>
+  <si>
+    <t>W.02.02</t>
+  </si>
+  <si>
+    <t>W.02.03</t>
+  </si>
+  <si>
+    <t>W.02.04</t>
+  </si>
+  <si>
+    <t>W.02.05</t>
+  </si>
+  <si>
+    <t>W.02.06</t>
+  </si>
+  <si>
+    <t>W.02.07</t>
+  </si>
+  <si>
+    <t>W.02.08</t>
+  </si>
+  <si>
+    <t>W.02.09</t>
+  </si>
+  <si>
+    <t>W.02.10</t>
+  </si>
+  <si>
+    <t>W.03.02</t>
+  </si>
+  <si>
+    <t>W.03.03</t>
+  </si>
+  <si>
+    <t>W.03.04</t>
+  </si>
+  <si>
+    <t>W.03.05</t>
+  </si>
+  <si>
+    <t>W.03.06</t>
+  </si>
+  <si>
+    <t>W.03.07</t>
+  </si>
+  <si>
+    <t>W.03.08</t>
+  </si>
+  <si>
+    <t>W.03.09</t>
+  </si>
+  <si>
+    <t>W.04.01</t>
+  </si>
+  <si>
+    <t>W.04.04</t>
+  </si>
+  <si>
+    <t>W.04.05</t>
+  </si>
+  <si>
+    <t>W.04.06</t>
+  </si>
+  <si>
+    <t>W.04.07</t>
+  </si>
+  <si>
+    <t>W.04.08</t>
+  </si>
+  <si>
+    <t>W.04.09</t>
+  </si>
+  <si>
+    <t>W.04.10</t>
+  </si>
+  <si>
+    <t>W.05.01</t>
+  </si>
+  <si>
+    <t>W.05.02</t>
+  </si>
+  <si>
+    <t>W.05.03</t>
+  </si>
+  <si>
+    <t>W.05.04</t>
+  </si>
+  <si>
+    <t>W.05.05</t>
+  </si>
+  <si>
+    <t>W.05.07</t>
+  </si>
+  <si>
+    <t>W.05.08</t>
+  </si>
+  <si>
+    <t>W.05.09</t>
+  </si>
+  <si>
+    <t>W.05.10</t>
+  </si>
+  <si>
+    <t>W.06.01</t>
+  </si>
+  <si>
+    <t>W.06.02</t>
+  </si>
+  <si>
+    <t>W.06.04</t>
+  </si>
+  <si>
+    <t>W.06.05</t>
+  </si>
+  <si>
+    <t>W.06.06</t>
+  </si>
+  <si>
+    <t>W.06.08</t>
+  </si>
+  <si>
+    <t>W.06.09</t>
+  </si>
+  <si>
+    <t>W.06.10</t>
+  </si>
+  <si>
+    <t>W.07.01</t>
+  </si>
+  <si>
+    <t>W.07.02</t>
+  </si>
+  <si>
+    <t>W.07.03</t>
+  </si>
+  <si>
+    <t>W.07.04</t>
+  </si>
+  <si>
+    <t>W.07.05</t>
+  </si>
+  <si>
+    <t>W.07.06</t>
+  </si>
+  <si>
+    <t>W.07.08</t>
+  </si>
+  <si>
+    <t>W.07.10</t>
+  </si>
+  <si>
+    <t>W.08.01</t>
+  </si>
+  <si>
+    <t>W.08.02</t>
+  </si>
+  <si>
+    <t>W.08.04</t>
+  </si>
+  <si>
+    <t>W.08.05</t>
+  </si>
+  <si>
+    <t>W.08.06</t>
+  </si>
+  <si>
+    <t>W.08.08</t>
+  </si>
+  <si>
+    <t>W.08.09</t>
+  </si>
+  <si>
+    <t>W.08.10</t>
+  </si>
+  <si>
+    <t>W.09.01</t>
+  </si>
+  <si>
+    <t>W.09.03</t>
+  </si>
+  <si>
+    <t>W.09.04</t>
+  </si>
+  <si>
+    <t>W.09.05</t>
+  </si>
+  <si>
+    <t>W.09.07</t>
+  </si>
+  <si>
+    <t>W.09.08</t>
+  </si>
+  <si>
+    <t>W.09.09</t>
+  </si>
+  <si>
+    <t>W.09.10</t>
+  </si>
+  <si>
+    <t>W.10.02</t>
+  </si>
+  <si>
+    <t>W.10.03</t>
+  </si>
+  <si>
+    <t>W.10.04</t>
+  </si>
+  <si>
+    <t>W.10.05</t>
+  </si>
+  <si>
+    <t>W.10.06</t>
+  </si>
+  <si>
+    <t>W.10.07</t>
+  </si>
+  <si>
+    <t>W.10.08</t>
+  </si>
+  <si>
+    <t>W.10.09</t>
+  </si>
+  <si>
+    <t>W.10.10</t>
+  </si>
+  <si>
+    <t>W.11.01</t>
+  </si>
+  <si>
+    <t>W.11.02</t>
+  </si>
+  <si>
+    <t>W.11.03</t>
+  </si>
+  <si>
+    <t>W.11.04</t>
+  </si>
+  <si>
+    <t>W.11.05</t>
+  </si>
+  <si>
+    <t>W.11.06</t>
+  </si>
+  <si>
+    <t>W.11.07</t>
+  </si>
+  <si>
+    <t>W.11.08</t>
+  </si>
+  <si>
+    <t>W.11.09</t>
+  </si>
+  <si>
+    <t>W.11.10</t>
+  </si>
+  <si>
+    <t>W.12.02</t>
+  </si>
+  <si>
+    <t>W.12.03</t>
+  </si>
+  <si>
+    <t>W.12.04</t>
+  </si>
+  <si>
+    <t>W.12.05</t>
+  </si>
+  <si>
+    <t>W.12.06</t>
+  </si>
+  <si>
+    <t>W.12.07</t>
+  </si>
+  <si>
+    <t>W.12.08</t>
+  </si>
+  <si>
+    <t>W.12.09</t>
+  </si>
+  <si>
+    <t>W.12.10</t>
+  </si>
+  <si>
+    <t>W.14.01</t>
+  </si>
+  <si>
+    <t>W.14.02</t>
+  </si>
+  <si>
+    <t>W.14.04</t>
+  </si>
+  <si>
+    <t>W.14.05</t>
+  </si>
+  <si>
+    <t>W.14.07</t>
+  </si>
+  <si>
+    <t>W.14.08</t>
+  </si>
+  <si>
+    <t>W.14.09</t>
+  </si>
+  <si>
+    <t>W.14.10</t>
+  </si>
+  <si>
+    <t>W.15.01</t>
+  </si>
+  <si>
+    <t>W.15.03</t>
+  </si>
+  <si>
+    <t>W.15.04</t>
+  </si>
+  <si>
+    <t>W.15.05</t>
+  </si>
+  <si>
+    <t>W.15.06</t>
+  </si>
+  <si>
+    <t>W.15.07</t>
+  </si>
+  <si>
+    <t>W.15.09</t>
+  </si>
+  <si>
+    <t>W.15.10</t>
+  </si>
+  <si>
+    <t>W.16.02</t>
+  </si>
+  <si>
+    <t>W.16.03</t>
+  </si>
+  <si>
+    <t>W.16.04</t>
+  </si>
+  <si>
+    <t>W.16.05</t>
+  </si>
+  <si>
+    <t>W.16.07</t>
+  </si>
+  <si>
+    <t>W.17.02</t>
+  </si>
+  <si>
+    <t>W.17.03</t>
+  </si>
+  <si>
+    <t>W.17.05</t>
+  </si>
+  <si>
+    <t>W.17.06</t>
+  </si>
+  <si>
+    <t>bql.4sriverside@khaservice.com.vn</t>
+  </si>
+  <si>
+    <t>Bql4sriverside@</t>
+  </si>
+  <si>
+    <t>CHUNG CƯ RIVA PARK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2586,6 +1926,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFDFE2E7"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2630,7 +1981,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2678,11 +2029,20 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3059,7 +2419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
@@ -3076,15 +2436,27 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>822</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="B2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="21"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="12"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="22"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{10830F82-A70C-4627-8C87-26099D50CBA3}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{95A0C2DA-4A6B-4758-8E1A-A128A6421E88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -3093,10 +2465,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B465"/>
+  <dimension ref="A1:B443"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" style="19" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3108,3729 +2480,2757 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A29" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A30" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A31" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A32" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A34" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A36" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A37" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A38" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A39" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A40" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A41" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A42" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A43" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A44" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A45" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A46" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A47" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A48" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A49" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A50" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A51" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A53" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A54" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A55" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A56" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A57" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A58" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A59" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A60" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A61" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A62" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A63" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A64" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A65" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A66" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A67" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A68" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A70" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A71" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="B71" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A72" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="B72" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A73" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="B73" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A74" s="20" t="s">
         <v>429</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="B74" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A75" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="B75" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A76" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="B76" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A77" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="B77" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A78" s="20" t="s">
         <v>433</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="B78" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A79" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>605</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="B79" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A80" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="B80" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A81" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="B81" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="B82" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A83" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="B83" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A84" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="B84" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A85" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="B85" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A86" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="B86" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A87" s="20" t="s">
         <v>442</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>606</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="B87" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A88" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="B88" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A89" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>607</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="B89" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A90" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
+      <c r="B90" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A91" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
+      <c r="B91" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A92" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
+      <c r="B92" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A93" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
+      <c r="B93" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A94" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="B94" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A95" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+      <c r="B95" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A96" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="B96" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A97" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
+      <c r="B97" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A98" s="20" t="s">
         <v>453</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
+      <c r="B98" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A99" s="20" t="s">
         <v>454</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
+      <c r="B99" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A100" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="B100" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A101" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
+      <c r="B101" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A102" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
+      <c r="B102" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A103" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
+      <c r="B103" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A104" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
+      <c r="B104" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A105" s="20" t="s">
         <v>460</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>598</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
+      <c r="B105" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A106" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
+      <c r="B106" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A107" s="20" t="s">
         <v>462</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
+      <c r="B107" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A108" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
+      <c r="B108" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A109" s="20" t="s">
         <v>464</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="18" t="s">
+      <c r="B109" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A110" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="18" t="s">
+      <c r="B110" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A111" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="18" t="s">
+      <c r="B111" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A112" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="18" t="s">
+      <c r="B112" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A113" s="20" t="s">
         <v>468</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="18" t="s">
+      <c r="B113" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A114" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="B54" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="18" t="s">
+      <c r="B114" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A115" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="18" t="s">
+      <c r="B115" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A116" s="20" t="s">
         <v>471</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="18" t="s">
+      <c r="B116" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A117" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="18" t="s">
-        <v>599</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="18" t="s">
+      <c r="B117" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A118" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="18" t="s">
+      <c r="B118" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A119" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
+      <c r="B119" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A120" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="B61" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="18" t="s">
+      <c r="B120" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A121" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="18" t="s">
+      <c r="B121" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A122" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="B63" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="18" t="s">
+      <c r="B122" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A123" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="18" t="s">
-        <v>610</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
+      <c r="B123" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A124" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="B66" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="18" t="s">
-        <v>600</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="18" t="s">
+      <c r="B124" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A125" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="18" t="s">
+      <c r="B125" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A126" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="18" t="s">
+      <c r="B126" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A127" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="18" t="s">
+      <c r="B127" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A128" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="B71" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="18" t="s">
+      <c r="B128" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A129" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="B72" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="18" t="s">
-        <v>601</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="18" t="s">
+      <c r="B129" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A130" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="B74" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="18" t="s">
+      <c r="B130" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A131" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="18" t="s">
+      <c r="B131" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A132" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="18" t="s">
+      <c r="B132" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A133" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="18" t="s">
+      <c r="B133" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A134" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="B78" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="B79" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="18" t="s">
+      <c r="B134" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A135" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="B80" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="18" t="s">
+      <c r="B135" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A136" s="20" t="s">
         <v>491</v>
       </c>
-      <c r="B81" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="18" t="s">
+      <c r="B136" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A137" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="B82" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="18" t="s">
+      <c r="B137" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A138" s="20" t="s">
         <v>493</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="18" t="s">
+      <c r="B138" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A139" s="20" t="s">
         <v>494</v>
       </c>
-      <c r="B84" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="18" t="s">
+      <c r="B139" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A140" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="B85" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="18" t="s">
+      <c r="B140" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A141" s="20" t="s">
         <v>496</v>
       </c>
-      <c r="B86" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="18" t="s">
+      <c r="B141" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A142" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="B87" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="18" t="s">
+      <c r="B142" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A143" s="20" t="s">
         <v>498</v>
       </c>
-      <c r="B88" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="18" t="s">
+      <c r="B143" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A144" s="20" t="s">
         <v>499</v>
       </c>
-      <c r="B89" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="18" t="s">
+      <c r="B144" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A145" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="B90" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="18" t="s">
+      <c r="B145" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A146" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="18" t="s">
+      <c r="B146" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A147" s="20" t="s">
         <v>502</v>
       </c>
-      <c r="B92" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="18" t="s">
+      <c r="B147" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A148" s="20" t="s">
         <v>503</v>
       </c>
-      <c r="B93" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="18" t="s">
+      <c r="B148" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A149" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="B94" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="18" t="s">
+      <c r="B149" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A150" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="B95" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="18" t="s">
+      <c r="B150" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A151" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="B96" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="18" t="s">
+      <c r="B151" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A152" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="18" t="s">
+      <c r="B152" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A153" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="B98" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="18" t="s">
+      <c r="B153" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A154" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="B99" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="18" t="s">
+      <c r="B154" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A155" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="B100" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="18" t="s">
+      <c r="B155" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A156" s="20" t="s">
         <v>511</v>
       </c>
-      <c r="B101" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="18" t="s">
+      <c r="B156" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A157" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="B102" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="B103" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="18" t="s">
+      <c r="B157" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A158" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="B104" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B105" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="18" t="s">
+      <c r="B158" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A159" s="20" t="s">
         <v>514</v>
       </c>
-      <c r="B106" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="18" t="s">
+      <c r="B159" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A160" s="20" t="s">
         <v>515</v>
       </c>
-      <c r="B107" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="18" t="s">
+      <c r="B160" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A161" s="20" t="s">
         <v>516</v>
       </c>
-      <c r="B108" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="18" t="s">
-        <v>612</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="18" t="s">
+      <c r="B161" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A162" s="20" t="s">
         <v>517</v>
       </c>
-      <c r="B111" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="18" t="s">
+      <c r="B162" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A163" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="B112" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="B113" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" s="18" t="s">
+      <c r="B163" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A164" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="B114" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" s="18" t="s">
+      <c r="B164" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A165" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="B115" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" s="18" t="s">
+      <c r="B165" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A166" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="B116" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="18" t="s">
+      <c r="B166" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A167" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="B117" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" s="18" t="s">
+      <c r="B167" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A168" s="20" t="s">
         <v>523</v>
       </c>
-      <c r="B118" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="18" t="s">
-        <v>613</v>
-      </c>
-      <c r="B119" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" s="18" t="s">
+      <c r="B168" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A169" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="B120" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" s="18" t="s">
+      <c r="B169" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A170" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="B121" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="18" t="s">
+      <c r="B170" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A171" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="B122" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="18" t="s">
+      <c r="B171" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A172" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="B123" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" s="18" t="s">
+      <c r="B172" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A173" s="20" t="s">
         <v>528</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" s="18" t="s">
+      <c r="B173" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A174" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" s="18" t="s">
+      <c r="B174" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A175" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="B127" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" s="18" t="s">
+      <c r="B175" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A176" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="B128" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" s="18" t="s">
+      <c r="B176" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A177" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="B129" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="18" t="s">
+      <c r="B177" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A178" s="20" t="s">
         <v>533</v>
       </c>
-      <c r="B130" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" s="18" t="s">
+      <c r="B178" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A179" s="20" t="s">
         <v>534</v>
       </c>
-      <c r="B131" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" s="18" t="s">
+      <c r="B179" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A180" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="B132" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="18" t="s">
+      <c r="B180" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A181" s="20" t="s">
         <v>536</v>
       </c>
-      <c r="B133" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="18" t="s">
-        <v>615</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="18" t="s">
+      <c r="B181" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A182" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" s="18" t="s">
+      <c r="B182" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A183" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="B136" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" s="18" t="s">
+      <c r="B183" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A184" s="20" t="s">
         <v>539</v>
       </c>
-      <c r="B137" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" s="18" t="s">
+      <c r="B184" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A185" s="20" t="s">
         <v>540</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" s="18" t="s">
+      <c r="B185" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A186" s="20" t="s">
         <v>541</v>
       </c>
-      <c r="B139" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" s="18" t="s">
+      <c r="B186" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A187" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="B140" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="B141" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="18" t="s">
+      <c r="B187" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A188" s="20" t="s">
         <v>543</v>
       </c>
-      <c r="B142" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143" s="18" t="s">
+      <c r="B188" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A189" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="B143" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="B144" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="18" t="s">
+      <c r="B189" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A190" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="B145" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="B146" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147" s="18" t="s">
-        <v>619</v>
-      </c>
-      <c r="B147" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" s="18" t="s">
+      <c r="B190" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A191" s="20" t="s">
         <v>546</v>
       </c>
-      <c r="B148" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" s="18" t="s">
+      <c r="B191" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A192" s="20" t="s">
         <v>547</v>
       </c>
-      <c r="B149" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" s="18" t="s">
+      <c r="B192" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A193" s="20" t="s">
         <v>548</v>
       </c>
-      <c r="B150" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="18" t="s">
+      <c r="B193" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A194" s="20" t="s">
         <v>549</v>
       </c>
-      <c r="B151" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="18" t="s">
+      <c r="B194" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A195" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="B152" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="18" t="s">
+      <c r="B195" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A196" s="20" t="s">
         <v>551</v>
       </c>
-      <c r="B153" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" s="18" t="s">
+      <c r="B196" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A197" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="B154" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B155" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" s="18" t="s">
+      <c r="B197" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A198" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="B156" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157" s="18" t="s">
+      <c r="B198" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A199" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="B157" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="18" t="s">
+      <c r="B199" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A200" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="B158" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="18" t="s">
+      <c r="B200" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A201" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="B159" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="B160" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="18" t="s">
-        <v>620</v>
-      </c>
-      <c r="B161" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="18" t="s">
-        <v>558</v>
-      </c>
-      <c r="B162" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="18" t="s">
-        <v>559</v>
-      </c>
-      <c r="B163" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="B164" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="18" t="s">
-        <v>561</v>
-      </c>
-      <c r="B165" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="B166" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="B167" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="B168" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="18" t="s">
-        <v>621</v>
-      </c>
-      <c r="B169" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="18" t="s">
-        <v>563</v>
-      </c>
-      <c r="B170" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="18" t="s">
-        <v>564</v>
-      </c>
-      <c r="B171" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="18" t="s">
-        <v>622</v>
-      </c>
-      <c r="B172" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173" s="18" t="s">
-        <v>565</v>
-      </c>
-      <c r="B173" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="18" t="s">
-        <v>566</v>
-      </c>
-      <c r="B174" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="18" t="s">
-        <v>567</v>
-      </c>
-      <c r="B175" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="18" t="s">
-        <v>568</v>
-      </c>
-      <c r="B176" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="18" t="s">
-        <v>623</v>
-      </c>
-      <c r="B177" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="18" t="s">
-        <v>569</v>
-      </c>
-      <c r="B178" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="18" t="s">
-        <v>570</v>
-      </c>
-      <c r="B179" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="B180" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="18" t="s">
-        <v>572</v>
-      </c>
-      <c r="B181" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="18" t="s">
-        <v>573</v>
-      </c>
-      <c r="B182" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="18" t="s">
-        <v>574</v>
-      </c>
-      <c r="B183" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="18" t="s">
-        <v>575</v>
-      </c>
-      <c r="B184" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="B185" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="18" t="s">
-        <v>577</v>
-      </c>
-      <c r="B186" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="18" t="s">
-        <v>578</v>
-      </c>
-      <c r="B187" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="18" t="s">
-        <v>579</v>
-      </c>
-      <c r="B188" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="B189" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="18" t="s">
-        <v>581</v>
-      </c>
-      <c r="B190" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="18" t="s">
-        <v>582</v>
-      </c>
-      <c r="B191" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="19" t="s">
-        <v>583</v>
-      </c>
-      <c r="B192" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="18" t="s">
-        <v>584</v>
-      </c>
-      <c r="B193" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="B194" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="18" t="s">
-        <v>586</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="18" t="s">
-        <v>587</v>
-      </c>
-      <c r="B196" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="18" t="s">
-        <v>588</v>
-      </c>
-      <c r="B197" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="18" t="s">
-        <v>589</v>
-      </c>
-      <c r="B198" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="18" t="s">
-        <v>590</v>
-      </c>
-      <c r="B199" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="18" t="s">
-        <v>591</v>
-      </c>
-      <c r="B200" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" s="18" t="s">
-        <v>592</v>
-      </c>
       <c r="B201" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="18" t="s">
-        <v>593</v>
+        <v>557</v>
       </c>
       <c r="B202" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="18" t="s">
-        <v>197</v>
+        <v>558</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="18" t="s">
-        <v>624</v>
+        <v>559</v>
       </c>
       <c r="B204" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="18" t="s">
-        <v>625</v>
+        <v>560</v>
       </c>
       <c r="B205" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="18" t="s">
-        <v>198</v>
+        <v>561</v>
       </c>
       <c r="B206" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="18" t="s">
-        <v>199</v>
+        <v>562</v>
       </c>
       <c r="B207" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="18" t="s">
-        <v>200</v>
+        <v>563</v>
       </c>
       <c r="B208" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="18" t="s">
-        <v>201</v>
+        <v>564</v>
       </c>
       <c r="B209" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="18" t="s">
-        <v>181</v>
+        <v>565</v>
       </c>
       <c r="B210" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="18" t="s">
-        <v>202</v>
+        <v>566</v>
       </c>
       <c r="B211" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="18" t="s">
-        <v>203</v>
+        <v>567</v>
       </c>
       <c r="B212" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="18" t="s">
-        <v>204</v>
+        <v>568</v>
       </c>
       <c r="B213" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="18" t="s">
-        <v>205</v>
+        <v>569</v>
       </c>
       <c r="B214" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="18" t="s">
-        <v>626</v>
+        <v>570</v>
       </c>
       <c r="B215" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="18" t="s">
-        <v>206</v>
+        <v>571</v>
       </c>
       <c r="B216" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="18" t="s">
-        <v>207</v>
+        <v>572</v>
       </c>
       <c r="B217" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="18" t="s">
-        <v>208</v>
+        <v>573</v>
       </c>
       <c r="B218" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="18" t="s">
-        <v>209</v>
+        <v>574</v>
       </c>
       <c r="B219" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="18" t="s">
-        <v>210</v>
+        <v>575</v>
       </c>
       <c r="B220" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="18" t="s">
-        <v>211</v>
+        <v>576</v>
       </c>
       <c r="B221" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="18" t="s">
-        <v>212</v>
+        <v>577</v>
       </c>
       <c r="B222" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="18" t="s">
-        <v>213</v>
+        <v>578</v>
       </c>
       <c r="B223" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="18" t="s">
-        <v>214</v>
+        <v>579</v>
       </c>
       <c r="B224" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="18" t="s">
-        <v>627</v>
+        <v>580</v>
       </c>
       <c r="B225" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="18" t="s">
-        <v>215</v>
+        <v>581</v>
       </c>
       <c r="B226" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="18" t="s">
-        <v>216</v>
+        <v>582</v>
       </c>
       <c r="B227" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="18" t="s">
-        <v>217</v>
+        <v>583</v>
       </c>
       <c r="B228" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="18" t="s">
-        <v>218</v>
+        <v>584</v>
       </c>
       <c r="B229" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="18" t="s">
-        <v>219</v>
+        <v>585</v>
       </c>
       <c r="B230" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="18" t="s">
-        <v>220</v>
+        <v>586</v>
       </c>
       <c r="B231" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="18" t="s">
-        <v>221</v>
+        <v>587</v>
       </c>
       <c r="B232" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="18" t="s">
-        <v>628</v>
+        <v>588</v>
       </c>
       <c r="B233" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="18" t="s">
-        <v>222</v>
+        <v>589</v>
       </c>
       <c r="B234" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="18" t="s">
-        <v>223</v>
+        <v>590</v>
       </c>
       <c r="B235" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="18" t="s">
-        <v>224</v>
+        <v>591</v>
       </c>
       <c r="B236" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="18" t="s">
-        <v>225</v>
+        <v>592</v>
       </c>
       <c r="B237" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="18" t="s">
-        <v>226</v>
+        <v>593</v>
       </c>
       <c r="B238" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="18" t="s">
-        <v>227</v>
+        <v>594</v>
       </c>
       <c r="B239" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="18" t="s">
-        <v>228</v>
+        <v>595</v>
       </c>
       <c r="B240" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="18" t="s">
-        <v>629</v>
+        <v>596</v>
       </c>
       <c r="B241" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="18" t="s">
-        <v>229</v>
+        <v>597</v>
       </c>
       <c r="B242" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="18" t="s">
-        <v>230</v>
+        <v>598</v>
       </c>
       <c r="B243" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="18" t="s">
-        <v>231</v>
+        <v>599</v>
       </c>
       <c r="B244" s="16" t="s">
-        <v>645</v>
+        <v>356</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A245" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="B245" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A245" s="18"/>
+      <c r="B245" s="16"/>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A246" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B246" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A246" s="18"/>
+      <c r="B246" s="16"/>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A247" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="B247" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A247" s="18"/>
+      <c r="B247" s="16"/>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A248" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="B248" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A248" s="18"/>
+      <c r="B248" s="16"/>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A249" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B249" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A249" s="18"/>
+      <c r="B249" s="16"/>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="B250" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A250" s="18"/>
+      <c r="B250" s="16"/>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="B251" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A251" s="18"/>
+      <c r="B251" s="16"/>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A252" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B252" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A252" s="18"/>
+      <c r="B252" s="16"/>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A253" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="B253" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A253" s="18"/>
+      <c r="B253" s="16"/>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A254" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B254" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A254" s="18"/>
+      <c r="B254" s="16"/>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A255" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="B255" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A255" s="18"/>
+      <c r="B255" s="16"/>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A256" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B256" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A256" s="18"/>
+      <c r="B256" s="16"/>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A257" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="B257" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A257" s="18"/>
+      <c r="B257" s="16"/>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A258" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B258" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A258" s="18"/>
+      <c r="B258" s="16"/>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A259" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="B259" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A259" s="18"/>
+      <c r="B259" s="16"/>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A260" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B260" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A260" s="18"/>
+      <c r="B260" s="16"/>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A261" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="B261" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A261" s="18"/>
+      <c r="B261" s="16"/>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A262" s="18" t="s">
-        <v>594</v>
-      </c>
-      <c r="B262" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A262" s="18"/>
+      <c r="B262" s="16"/>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A263" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B263" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A263" s="18"/>
+      <c r="B263" s="16"/>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A264" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="B264" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A264" s="18"/>
+      <c r="B264" s="16"/>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A265" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="B265" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A265" s="18"/>
+      <c r="B265" s="16"/>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A266" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B266" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A266" s="18"/>
+      <c r="B266" s="16"/>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A267" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B267" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A267" s="18"/>
+      <c r="B267" s="16"/>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A268" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="B268" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A268" s="18"/>
+      <c r="B268" s="16"/>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A269" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="B269" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A269" s="18"/>
+      <c r="B269" s="16"/>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A270" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B270" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A270" s="18"/>
+      <c r="B270" s="16"/>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A271" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="B271" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A271" s="18"/>
+      <c r="B271" s="16"/>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A272" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="B272" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A272" s="18"/>
+      <c r="B272" s="16"/>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="B273" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A273" s="18"/>
+      <c r="B273" s="16"/>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A274" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="B274" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A274" s="18"/>
+      <c r="B274" s="16"/>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A275" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B275" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A275" s="18"/>
+      <c r="B275" s="16"/>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="B276" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A276" s="18"/>
+      <c r="B276" s="16"/>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A277" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="B277" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A277" s="18"/>
+      <c r="B277" s="16"/>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A278" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="B278" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A278" s="18"/>
+      <c r="B278" s="16"/>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A279" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="B279" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A279" s="18"/>
+      <c r="B279" s="16"/>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A280" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B280" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A280" s="18"/>
+      <c r="B280" s="16"/>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A281" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B281" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A281" s="18"/>
+      <c r="B281" s="16"/>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A282" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="B282" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A282" s="18"/>
+      <c r="B282" s="16"/>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A283" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="B283" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A283" s="18"/>
+      <c r="B283" s="16"/>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A284" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B284" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A284" s="18"/>
+      <c r="B284" s="16"/>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A285" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B285" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A285" s="18"/>
+      <c r="B285" s="16"/>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A286" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B286" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A286" s="18"/>
+      <c r="B286" s="16"/>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A287" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="B287" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A287" s="18"/>
+      <c r="B287" s="16"/>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A288" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B288" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A288" s="18"/>
+      <c r="B288" s="16"/>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A289" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="B289" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A289" s="18"/>
+      <c r="B289" s="16"/>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A290" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B290" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A290" s="18"/>
+      <c r="B290" s="16"/>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A291" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="B291" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A291" s="18"/>
+      <c r="B291" s="16"/>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A292" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="B292" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A292" s="18"/>
+      <c r="B292" s="16"/>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A293" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="B293" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A293" s="18"/>
+      <c r="B293" s="16"/>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A294" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="B294" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A294" s="18"/>
+      <c r="B294" s="16"/>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A295" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="B295" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A295" s="18"/>
+      <c r="B295" s="16"/>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A296" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="B296" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A296" s="18"/>
+      <c r="B296" s="16"/>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A297" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="B297" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A297" s="18"/>
+      <c r="B297" s="16"/>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A298" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="B298" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A298" s="18"/>
+      <c r="B298" s="16"/>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A299" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="B299" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A299" s="18"/>
+      <c r="B299" s="16"/>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A300" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="B300" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A300" s="18"/>
+      <c r="B300" s="16"/>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A301" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="B301" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A301" s="18"/>
+      <c r="B301" s="16"/>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A302" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="B302" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A302" s="18"/>
+      <c r="B302" s="16"/>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A303" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="B303" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A303" s="18"/>
+      <c r="B303" s="16"/>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A304" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="B304" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A304" s="18"/>
+      <c r="B304" s="16"/>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A305" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="B305" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A305" s="18"/>
+      <c r="B305" s="16"/>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A306" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="B306" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A306" s="18"/>
+      <c r="B306" s="16"/>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A307" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="B307" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A307" s="18"/>
+      <c r="B307" s="16"/>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A308" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="B308" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A308" s="18"/>
+      <c r="B308" s="16"/>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A309" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B309" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A309" s="18"/>
+      <c r="B309" s="16"/>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A310" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B310" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A310" s="18"/>
+      <c r="B310" s="16"/>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A311" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="B311" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A311" s="18"/>
+      <c r="B311" s="16"/>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A312" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="B312" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A312" s="18"/>
+      <c r="B312" s="16"/>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A313" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="B313" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A313" s="18"/>
+      <c r="B313" s="16"/>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A314" s="18" t="s">
-        <v>634</v>
-      </c>
-      <c r="B314" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A314" s="18"/>
+      <c r="B314" s="16"/>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A315" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="B315" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A315" s="18"/>
+      <c r="B315" s="16"/>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A316" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B316" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A316" s="18"/>
+      <c r="B316" s="16"/>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A317" s="18" t="s">
-        <v>635</v>
-      </c>
-      <c r="B317" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A317" s="18"/>
+      <c r="B317" s="16"/>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A318" s="18" t="s">
-        <v>636</v>
-      </c>
-      <c r="B318" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A318" s="18"/>
+      <c r="B318" s="16"/>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A319" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="B319" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A319" s="18"/>
+      <c r="B319" s="16"/>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A320" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B320" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A320" s="18"/>
+      <c r="B320" s="16"/>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A321" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B321" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A321" s="18"/>
+      <c r="B321" s="16"/>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A322" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="B322" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A322" s="18"/>
+      <c r="B322" s="16"/>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A323" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="B323" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A323" s="18"/>
+      <c r="B323" s="16"/>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A324" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="B324" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A324" s="18"/>
+      <c r="B324" s="16"/>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A325" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="B325" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A325" s="18"/>
+      <c r="B325" s="16"/>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A326" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="B326" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A326" s="18"/>
+      <c r="B326" s="16"/>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A327" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="B327" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A327" s="18"/>
+      <c r="B327" s="16"/>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A328" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="B328" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A328" s="18"/>
+      <c r="B328" s="16"/>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A329" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B329" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A329" s="18"/>
+      <c r="B329" s="16"/>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A330" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="B330" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A330" s="18"/>
+      <c r="B330" s="16"/>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A331" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="B331" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A331" s="18"/>
+      <c r="B331" s="16"/>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A332" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="B332" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A332" s="18"/>
+      <c r="B332" s="16"/>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A333" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B333" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A333" s="18"/>
+      <c r="B333" s="16"/>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A334" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B334" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A334" s="18"/>
+      <c r="B334" s="16"/>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A335" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="B335" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A335" s="18"/>
+      <c r="B335" s="16"/>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A336" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B336" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A336" s="18"/>
+      <c r="B336" s="16"/>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A337" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B337" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A337" s="18"/>
+      <c r="B337" s="16"/>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A338" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B338" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A338" s="18"/>
+      <c r="B338" s="16"/>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A339" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="B339" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A339" s="18"/>
+      <c r="B339" s="16"/>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A340" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="B340" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A340" s="18"/>
+      <c r="B340" s="16"/>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A341" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="B341" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A341" s="18"/>
+      <c r="B341" s="16"/>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A342" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="B342" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A342" s="18"/>
+      <c r="B342" s="16"/>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A343" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="B343" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A343" s="18"/>
+      <c r="B343" s="16"/>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A344" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="B344" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A344" s="18"/>
+      <c r="B344" s="16"/>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A345" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="B345" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A345" s="18"/>
+      <c r="B345" s="16"/>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A346" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="B346" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A346" s="18"/>
+      <c r="B346" s="16"/>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A347" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B347" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A347" s="18"/>
+      <c r="B347" s="16"/>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A348" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="B348" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A348" s="18"/>
+      <c r="B348" s="16"/>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A349" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="B349" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A349" s="18"/>
+      <c r="B349" s="16"/>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A350" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="B350" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A350" s="18"/>
+      <c r="B350" s="16"/>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A351" s="18" t="s">
-        <v>637</v>
-      </c>
-      <c r="B351" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A351" s="18"/>
+      <c r="B351" s="16"/>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A352" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="B352" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A352" s="18"/>
+      <c r="B352" s="16"/>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A353" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="B353" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A353" s="18"/>
+      <c r="B353" s="16"/>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A354" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="B354" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A354" s="18"/>
+      <c r="B354" s="16"/>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A355" s="18" t="s">
-        <v>638</v>
-      </c>
-      <c r="B355" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A355" s="18"/>
+      <c r="B355" s="16"/>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A356" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="B356" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A356" s="18"/>
+      <c r="B356" s="16"/>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A357" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="B357" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A357" s="18"/>
+      <c r="B357" s="16"/>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A358" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="B358" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A358" s="18"/>
+      <c r="B358" s="16"/>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A359" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="B359" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A359" s="18"/>
+      <c r="B359" s="16"/>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A360" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="B360" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A360" s="18"/>
+      <c r="B360" s="16"/>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A361" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="B361" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A361" s="18"/>
+      <c r="B361" s="16"/>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A362" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="B362" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A362" s="18"/>
+      <c r="B362" s="16"/>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A363" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="B363" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A363" s="18"/>
+      <c r="B363" s="16"/>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A364" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="B364" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A364" s="18"/>
+      <c r="B364" s="16"/>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A365" s="18" t="s">
-        <v>639</v>
-      </c>
-      <c r="B365" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A365" s="18"/>
+      <c r="B365" s="16"/>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A366" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="B366" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A366" s="18"/>
+      <c r="B366" s="16"/>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A367" s="18" t="s">
-        <v>640</v>
-      </c>
-      <c r="B367" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A367" s="18"/>
+      <c r="B367" s="16"/>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A368" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="B368" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A368" s="18"/>
+      <c r="B368" s="16"/>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A369" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="B369" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A369" s="18"/>
+      <c r="B369" s="16"/>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A370" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="B370" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A370" s="18"/>
+      <c r="B370" s="16"/>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A371" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="B371" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A371" s="18"/>
+      <c r="B371" s="16"/>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A372" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="B372" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A372" s="18"/>
+      <c r="B372" s="16"/>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A373" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="B373" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A373" s="18"/>
+      <c r="B373" s="16"/>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A374" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B374" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A374" s="18"/>
+      <c r="B374" s="16"/>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A375" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="B375" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A375" s="18"/>
+      <c r="B375" s="16"/>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A376" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="B376" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A376" s="18"/>
+      <c r="B376" s="16"/>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A377" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="B377" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A377" s="18"/>
+      <c r="B377" s="16"/>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A378" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="B378" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A378" s="18"/>
+      <c r="B378" s="16"/>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A379" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="B379" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A379" s="18"/>
+      <c r="B379" s="16"/>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A380" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="B380" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A380" s="18"/>
+      <c r="B380" s="16"/>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A381" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="B381" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A381" s="18"/>
+      <c r="B381" s="16"/>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A382" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="B382" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A382" s="18"/>
+      <c r="B382" s="16"/>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A383" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="B383" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A383" s="18"/>
+      <c r="B383" s="16"/>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A384" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B384" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A384" s="18"/>
+      <c r="B384" s="16"/>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A385" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="B385" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A385" s="18"/>
+      <c r="B385" s="16"/>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A386" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="B386" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A386" s="18"/>
+      <c r="B386" s="16"/>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A387" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="B387" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A387" s="18"/>
+      <c r="B387" s="16"/>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A388" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="B388" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A388" s="18"/>
+      <c r="B388" s="16"/>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A389" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="B389" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A389" s="18"/>
+      <c r="B389" s="16"/>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A390" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="B390" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A390" s="18"/>
+      <c r="B390" s="16"/>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A391" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="B391" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A391" s="18"/>
+      <c r="B391" s="16"/>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A392" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="B392" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A392" s="18"/>
+      <c r="B392" s="16"/>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A393" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B393" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A393" s="18"/>
+      <c r="B393" s="16"/>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A394" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="B394" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A394" s="18"/>
+      <c r="B394" s="16"/>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A395" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="B395" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A395" s="18"/>
+      <c r="B395" s="16"/>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A396" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="B396" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A396" s="18"/>
+      <c r="B396" s="16"/>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A397" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B397" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A397" s="18"/>
+      <c r="B397" s="16"/>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A398" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="B398" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A398" s="18"/>
+      <c r="B398" s="16"/>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A399" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="B399" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A399" s="18"/>
+      <c r="B399" s="16"/>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A400" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="B400" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A400" s="18"/>
+      <c r="B400" s="16"/>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A401" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="B401" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A401" s="18"/>
+      <c r="B401" s="16"/>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A402" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="B402" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A402" s="18"/>
+      <c r="B402" s="16"/>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A403" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="B403" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A403" s="18"/>
+      <c r="B403" s="16"/>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A404" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="B404" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A404" s="18"/>
+      <c r="B404" s="16"/>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A405" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="B405" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A405" s="18"/>
+      <c r="B405" s="16"/>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A406" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="B406" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A406" s="18"/>
+      <c r="B406" s="16"/>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A407" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="B407" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A407" s="18"/>
+      <c r="B407" s="16"/>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A408" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="B408" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A408" s="18"/>
+      <c r="B408" s="16"/>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A409" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="B409" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A409" s="18"/>
+      <c r="B409" s="16"/>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A410" s="18" t="s">
-        <v>641</v>
-      </c>
-      <c r="B410" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A410" s="18"/>
+      <c r="B410" s="16"/>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A411" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="B411" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A411" s="18"/>
+      <c r="B411" s="16"/>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A412" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="B412" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A412" s="18"/>
+      <c r="B412" s="16"/>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A413" s="18" t="s">
-        <v>642</v>
-      </c>
-      <c r="B413" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A413" s="18"/>
+      <c r="B413" s="16"/>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A414" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="B414" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A414" s="18"/>
+      <c r="B414" s="16"/>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A415" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="B415" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A415" s="18"/>
+      <c r="B415" s="16"/>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A416" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="B416" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A416" s="18"/>
+      <c r="B416" s="16"/>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A417" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="B417" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A417" s="18"/>
+      <c r="B417" s="16"/>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A418" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="B418" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A418" s="18"/>
+      <c r="B418" s="16"/>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A419" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="B419" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A419" s="18"/>
+      <c r="B419" s="16"/>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A420" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="B420" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A420" s="18"/>
+      <c r="B420" s="16"/>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A421" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="B421" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A421" s="18"/>
+      <c r="B421" s="16"/>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A422" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="B422" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A422" s="18"/>
+      <c r="B422" s="16"/>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A423" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="B423" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A423" s="18"/>
+      <c r="B423" s="16"/>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A424" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="B424" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A424" s="18"/>
+      <c r="B424" s="16"/>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A425" s="18" t="s">
-        <v>643</v>
-      </c>
-      <c r="B425" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A425" s="18"/>
+      <c r="B425" s="16"/>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A426" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="B426" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A426" s="18"/>
+      <c r="B426" s="16"/>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A427" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="B427" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A427" s="18"/>
+      <c r="B427" s="16"/>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A428" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="B428" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A428" s="18"/>
+      <c r="B428" s="16"/>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A429" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="B429" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A429" s="18"/>
+      <c r="B429" s="16"/>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A430" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="B430" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A430" s="18"/>
+      <c r="B430" s="16"/>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A431" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="B431" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A431" s="18"/>
+      <c r="B431" s="16"/>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A432" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="B432" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A432" s="18"/>
+      <c r="B432" s="16"/>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A433" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="B433" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A433" s="18"/>
+      <c r="B433" s="16"/>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A434" s="18" t="s">
-        <v>397</v>
-      </c>
-      <c r="B434" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A434" s="18"/>
+      <c r="B434" s="16"/>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A435" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B435" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A435" s="18"/>
+      <c r="B435" s="16"/>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A436" s="18" t="s">
-        <v>398</v>
-      </c>
-      <c r="B436" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A436" s="18"/>
+      <c r="B436" s="16"/>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A437" s="18" t="s">
-        <v>399</v>
-      </c>
-      <c r="B437" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A437" s="18"/>
+      <c r="B437" s="16"/>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A438" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="B438" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A438" s="18"/>
+      <c r="B438" s="16"/>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A439" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="B439" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A439" s="18"/>
+      <c r="B439" s="16"/>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A440" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="B440" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A440" s="18"/>
+      <c r="B440" s="16"/>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A441" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="B441" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A441" s="18"/>
+      <c r="B441" s="16"/>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A442" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="B442" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A442" s="18"/>
+      <c r="B442" s="16"/>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A443" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="B443" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A444" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="B444" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A445" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="B445" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A446" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="B446" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A447" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="B447" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A448" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="B448" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A449" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="B449" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A450" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="B450" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A451" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="B451" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A452" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="B452" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A453" s="18" t="s">
-        <v>644</v>
-      </c>
-      <c r="B453" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A454" s="18" t="s">
-        <v>414</v>
-      </c>
-      <c r="B454" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A455" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="B455" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A456" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="B456" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A457" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="B457" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A458" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="B458" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A459" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="B459" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A460" s="18" t="s">
-        <v>420</v>
-      </c>
-      <c r="B460" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A461" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="B461" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A462" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="B462" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A463" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="B463" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A464" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="B464" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A465" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="B465" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="A443" s="18"/>
+      <c r="B443" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C223" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C223">
-      <sortCondition sortBy="cellColor" ref="A1:A223" dxfId="5"/>
+  <autoFilter ref="A1:C201" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C201">
+      <sortCondition sortBy="cellColor" ref="A1:A201" dxfId="5"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="A1 E1:E1048576 A466:A1048576">
+  <conditionalFormatting sqref="A444:A1048576 A1 E1:E1048576">
     <cfRule type="duplicateValues" dxfId="4" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A466:A1048576 A1">
+  <conditionalFormatting sqref="A444:A1048576 A1">
     <cfRule type="duplicateValues" dxfId="3" priority="33"/>
     <cfRule type="duplicateValues" dxfId="2" priority="34"/>
     <cfRule type="duplicateValues" dxfId="1" priority="35"/>
@@ -6861,7 +5261,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>646</v>
+        <v>181</v>
       </c>
       <c r="B2" s="11">
         <v>4</v>
@@ -6869,7 +5269,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>647</v>
+        <v>182</v>
       </c>
       <c r="B3" s="11">
         <v>0</v>
@@ -6877,7 +5277,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>648</v>
+        <v>183</v>
       </c>
       <c r="B4" s="11">
         <v>3</v>
@@ -6885,7 +5285,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>649</v>
+        <v>184</v>
       </c>
       <c r="B5" s="11">
         <v>0</v>
@@ -6893,7 +5293,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>650</v>
+        <v>185</v>
       </c>
       <c r="B6" s="11">
         <v>3</v>
@@ -6901,7 +5301,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>651</v>
+        <v>186</v>
       </c>
       <c r="B7" s="11">
         <v>0</v>
@@ -6909,7 +5309,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>652</v>
+        <v>187</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -6917,7 +5317,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>653</v>
+        <v>188</v>
       </c>
       <c r="B9" s="11">
         <v>0</v>
@@ -6925,7 +5325,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>654</v>
+        <v>189</v>
       </c>
       <c r="B10" s="11">
         <v>4</v>
@@ -6933,7 +5333,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>655</v>
+        <v>190</v>
       </c>
       <c r="B11" s="11">
         <v>0</v>
@@ -6941,7 +5341,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>656</v>
+        <v>191</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -6949,7 +5349,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>657</v>
+        <v>192</v>
       </c>
       <c r="B13" s="11">
         <v>7</v>
@@ -6957,7 +5357,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>658</v>
+        <v>193</v>
       </c>
       <c r="B14" s="11">
         <v>0</v>
@@ -6965,7 +5365,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>659</v>
+        <v>194</v>
       </c>
       <c r="B15" s="11">
         <v>1</v>
@@ -6973,7 +5373,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>660</v>
+        <v>195</v>
       </c>
       <c r="B16" s="11">
         <v>0</v>
@@ -6981,7 +5381,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>661</v>
+        <v>196</v>
       </c>
       <c r="B17" s="11">
         <v>2</v>
@@ -6989,7 +5389,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>662</v>
+        <v>197</v>
       </c>
       <c r="B18" s="11">
         <v>4</v>
@@ -6997,7 +5397,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>663</v>
+        <v>198</v>
       </c>
       <c r="B19" s="11">
         <v>0</v>
@@ -7005,7 +5405,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>664</v>
+        <v>199</v>
       </c>
       <c r="B20" s="11">
         <v>3</v>
@@ -7013,7 +5413,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>665</v>
+        <v>200</v>
       </c>
       <c r="B21" s="11">
         <v>1</v>
@@ -7021,7 +5421,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>666</v>
+        <v>201</v>
       </c>
       <c r="B22" s="11">
         <v>3</v>
@@ -7029,7 +5429,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>667</v>
+        <v>202</v>
       </c>
       <c r="B23" s="11">
         <v>5</v>
@@ -7037,7 +5437,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>668</v>
+        <v>203</v>
       </c>
       <c r="B24" s="11">
         <v>0</v>
@@ -7045,7 +5445,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>669</v>
+        <v>204</v>
       </c>
       <c r="B25" s="11">
         <v>2</v>
@@ -7053,7 +5453,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>670</v>
+        <v>205</v>
       </c>
       <c r="B26" s="11">
         <v>0</v>
@@ -7061,7 +5461,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>671</v>
+        <v>206</v>
       </c>
       <c r="B27" s="11">
         <v>2</v>
@@ -7069,7 +5469,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>672</v>
+        <v>207</v>
       </c>
       <c r="B28" s="11">
         <v>0</v>
@@ -7077,7 +5477,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>673</v>
+        <v>208</v>
       </c>
       <c r="B29" s="11">
         <v>4</v>
@@ -7085,7 +5485,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>674</v>
+        <v>209</v>
       </c>
       <c r="B30" s="11">
         <v>2</v>
@@ -7093,7 +5493,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>675</v>
+        <v>210</v>
       </c>
       <c r="B31" s="11">
         <v>0</v>
@@ -7101,7 +5501,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>676</v>
+        <v>211</v>
       </c>
       <c r="B32" s="11">
         <v>3</v>
@@ -7109,7 +5509,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>677</v>
+        <v>212</v>
       </c>
       <c r="B33" s="11">
         <v>4</v>
@@ -7117,7 +5517,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>678</v>
+        <v>213</v>
       </c>
       <c r="B34" s="11">
         <v>3</v>
@@ -7125,7 +5525,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>679</v>
+        <v>214</v>
       </c>
       <c r="B35" s="11">
         <v>0</v>
@@ -7133,7 +5533,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>680</v>
+        <v>215</v>
       </c>
       <c r="B36" s="11">
         <v>1</v>
@@ -7141,7 +5541,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>681</v>
+        <v>216</v>
       </c>
       <c r="B37" s="11">
         <v>4</v>
@@ -7149,7 +5549,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>682</v>
+        <v>217</v>
       </c>
       <c r="B38" s="11">
         <v>1</v>
@@ -7157,7 +5557,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>683</v>
+        <v>218</v>
       </c>
       <c r="B39" s="11">
         <v>2</v>
@@ -7165,7 +5565,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>684</v>
+        <v>219</v>
       </c>
       <c r="B40" s="11">
         <v>0</v>
@@ -7173,7 +5573,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>685</v>
+        <v>220</v>
       </c>
       <c r="B41" s="11">
         <v>1</v>
@@ -7181,7 +5581,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>686</v>
+        <v>221</v>
       </c>
       <c r="B42" s="11">
         <v>4</v>
@@ -7189,7 +5589,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>687</v>
+        <v>222</v>
       </c>
       <c r="B43" s="11">
         <v>3</v>
@@ -7197,7 +5597,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>688</v>
+        <v>223</v>
       </c>
       <c r="B44" s="11">
         <v>2</v>
@@ -7205,7 +5605,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>689</v>
+        <v>224</v>
       </c>
       <c r="B45" s="11">
         <v>0</v>
@@ -7213,7 +5613,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>690</v>
+        <v>225</v>
       </c>
       <c r="B46" s="11">
         <v>3</v>
@@ -7221,7 +5621,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>691</v>
+        <v>226</v>
       </c>
       <c r="B47" s="11">
         <v>2</v>
@@ -7229,7 +5629,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>692</v>
+        <v>227</v>
       </c>
       <c r="B48" s="11">
         <v>0</v>
@@ -7237,7 +5637,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>693</v>
+        <v>228</v>
       </c>
       <c r="B49" s="11">
         <v>1</v>
@@ -7245,7 +5645,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>694</v>
+        <v>229</v>
       </c>
       <c r="B50" s="11">
         <v>3</v>
@@ -7253,7 +5653,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>695</v>
+        <v>230</v>
       </c>
       <c r="B51" s="11">
         <v>0</v>
@@ -7261,7 +5661,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>696</v>
+        <v>231</v>
       </c>
       <c r="B52" s="11">
         <v>3</v>
@@ -7269,7 +5669,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>697</v>
+        <v>232</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -7277,7 +5677,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>698</v>
+        <v>233</v>
       </c>
       <c r="B54" s="11">
         <v>4</v>
@@ -7285,7 +5685,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>699</v>
+        <v>234</v>
       </c>
       <c r="B55" s="11">
         <v>0</v>
@@ -7293,7 +5693,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>700</v>
+        <v>235</v>
       </c>
       <c r="B56" s="11">
         <v>3</v>
@@ -7301,7 +5701,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>701</v>
+        <v>236</v>
       </c>
       <c r="B57" s="11">
         <v>0</v>
@@ -7309,7 +5709,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>702</v>
+        <v>237</v>
       </c>
       <c r="B58" s="11">
         <v>4</v>
@@ -7317,7 +5717,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>703</v>
+        <v>238</v>
       </c>
       <c r="B59" s="11">
         <v>3</v>
@@ -7325,7 +5725,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>704</v>
+        <v>239</v>
       </c>
       <c r="B60" s="11">
         <v>2</v>
@@ -7333,7 +5733,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>705</v>
+        <v>240</v>
       </c>
       <c r="B61" s="11">
         <v>3</v>
@@ -7341,7 +5741,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>706</v>
+        <v>241</v>
       </c>
       <c r="B62" s="11">
         <v>5</v>
@@ -7349,7 +5749,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>707</v>
+        <v>242</v>
       </c>
       <c r="B63" s="11">
         <v>0</v>
@@ -7357,7 +5757,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>708</v>
+        <v>243</v>
       </c>
       <c r="B64" s="11">
         <v>4</v>
@@ -7365,7 +5765,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>709</v>
+        <v>244</v>
       </c>
       <c r="B65" s="11">
         <v>0</v>
@@ -7373,7 +5773,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>710</v>
+        <v>245</v>
       </c>
       <c r="B66" s="11">
         <v>3</v>
@@ -7381,7 +5781,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>711</v>
+        <v>246</v>
       </c>
       <c r="B67" s="11">
         <v>0</v>
@@ -7389,7 +5789,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
-        <v>712</v>
+        <v>247</v>
       </c>
       <c r="B68" s="11">
         <v>4</v>
@@ -7397,7 +5797,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>713</v>
+        <v>248</v>
       </c>
       <c r="B69" s="11">
         <v>3</v>
@@ -7405,7 +5805,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>714</v>
+        <v>249</v>
       </c>
       <c r="B70" s="11">
         <v>5</v>
@@ -7413,7 +5813,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>715</v>
+        <v>250</v>
       </c>
       <c r="B71" s="11">
         <v>0</v>
@@ -7421,7 +5821,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>716</v>
+        <v>251</v>
       </c>
       <c r="B72" s="11">
         <v>3</v>
@@ -7429,7 +5829,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>717</v>
+        <v>252</v>
       </c>
       <c r="B73" s="11">
         <v>1</v>
@@ -7437,7 +5837,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>718</v>
+        <v>253</v>
       </c>
       <c r="B74" s="11">
         <v>0</v>
@@ -7445,7 +5845,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>719</v>
+        <v>254</v>
       </c>
       <c r="B75" s="11">
         <v>3</v>
@@ -7453,7 +5853,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>720</v>
+        <v>255</v>
       </c>
       <c r="B76" s="11">
         <v>0</v>
@@ -7461,7 +5861,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
-        <v>721</v>
+        <v>256</v>
       </c>
       <c r="B77" s="11">
         <v>2</v>
@@ -7469,7 +5869,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>722</v>
+        <v>257</v>
       </c>
       <c r="B78" s="11">
         <v>3</v>
@@ -7477,7 +5877,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
-        <v>723</v>
+        <v>258</v>
       </c>
       <c r="B79" s="11">
         <v>0</v>
@@ -7485,7 +5885,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>724</v>
+        <v>259</v>
       </c>
       <c r="B80" s="11">
         <v>3</v>
@@ -7493,7 +5893,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
-        <v>725</v>
+        <v>260</v>
       </c>
       <c r="B81" s="11">
         <v>4</v>
@@ -7501,7 +5901,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
-        <v>726</v>
+        <v>261</v>
       </c>
       <c r="B82" s="11">
         <v>3</v>
@@ -7509,7 +5909,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>727</v>
+        <v>262</v>
       </c>
       <c r="B83" s="11">
         <v>0</v>
@@ -7517,7 +5917,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>728</v>
+        <v>263</v>
       </c>
       <c r="B84" s="11">
         <v>4</v>
@@ -7525,7 +5925,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>729</v>
+        <v>264</v>
       </c>
       <c r="B85" s="11">
         <v>2</v>
@@ -7533,7 +5933,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>730</v>
+        <v>265</v>
       </c>
       <c r="B86" s="11">
         <v>4</v>
@@ -7541,7 +5941,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
-        <v>731</v>
+        <v>266</v>
       </c>
       <c r="B87" s="11">
         <v>3</v>
@@ -7549,7 +5949,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>732</v>
+        <v>267</v>
       </c>
       <c r="B88" s="11">
         <v>2</v>
@@ -7557,7 +5957,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
-        <v>733</v>
+        <v>268</v>
       </c>
       <c r="B89" s="11">
         <v>0</v>
@@ -7565,7 +5965,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
-        <v>734</v>
+        <v>269</v>
       </c>
       <c r="B90" s="11">
         <v>1</v>
@@ -7573,7 +5973,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
-        <v>735</v>
+        <v>270</v>
       </c>
       <c r="B91" s="11">
         <v>0</v>
@@ -7581,7 +5981,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
-        <v>736</v>
+        <v>271</v>
       </c>
       <c r="B92" s="11">
         <v>4</v>
@@ -7589,7 +5989,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
-        <v>737</v>
+        <v>272</v>
       </c>
       <c r="B93" s="11">
         <v>0</v>
@@ -7597,7 +5997,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
-        <v>738</v>
+        <v>273</v>
       </c>
       <c r="B94" s="11">
         <v>2</v>
@@ -7605,7 +6005,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>739</v>
+        <v>274</v>
       </c>
       <c r="B95" s="11">
         <v>0</v>
@@ -7613,7 +6013,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
-        <v>740</v>
+        <v>275</v>
       </c>
       <c r="B96" s="11">
         <v>4</v>
@@ -7621,7 +6021,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>741</v>
+        <v>276</v>
       </c>
       <c r="B97" s="11">
         <v>0</v>
@@ -7629,7 +6029,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
-        <v>742</v>
+        <v>277</v>
       </c>
       <c r="B98" s="11">
         <v>4</v>
@@ -7637,7 +6037,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>743</v>
+        <v>278</v>
       </c>
       <c r="B99" s="11">
         <v>0</v>
@@ -7645,7 +6045,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
-        <v>744</v>
+        <v>279</v>
       </c>
       <c r="B100" s="11">
         <v>3</v>
@@ -7653,7 +6053,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
-        <v>745</v>
+        <v>280</v>
       </c>
       <c r="B101" s="11">
         <v>4</v>
@@ -7661,7 +6061,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
-        <v>746</v>
+        <v>281</v>
       </c>
       <c r="B102" s="11">
         <v>8</v>
@@ -7669,7 +6069,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
-        <v>747</v>
+        <v>282</v>
       </c>
       <c r="B103" s="11">
         <v>3</v>
@@ -7677,7 +6077,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
-        <v>748</v>
+        <v>283</v>
       </c>
       <c r="B104" s="11">
         <v>0</v>
@@ -7685,7 +6085,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
-        <v>749</v>
+        <v>284</v>
       </c>
       <c r="B105" s="11">
         <v>0</v>
@@ -7693,7 +6093,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>750</v>
+        <v>285</v>
       </c>
       <c r="B106" s="11">
         <v>5</v>
@@ -7701,7 +6101,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
-        <v>751</v>
+        <v>286</v>
       </c>
       <c r="B107" s="11">
         <v>2</v>
@@ -7709,7 +6109,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
-        <v>752</v>
+        <v>287</v>
       </c>
       <c r="B108" s="11">
         <v>3</v>
@@ -7717,7 +6117,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
-        <v>753</v>
+        <v>288</v>
       </c>
       <c r="B109" s="11">
         <v>0</v>
@@ -7725,7 +6125,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
-        <v>754</v>
+        <v>289</v>
       </c>
       <c r="B110" s="11">
         <v>0</v>
@@ -7733,7 +6133,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>755</v>
+        <v>290</v>
       </c>
       <c r="B111" s="11">
         <v>3</v>
@@ -7741,7 +6141,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="11" t="s">
-        <v>756</v>
+        <v>291</v>
       </c>
       <c r="B112" s="11">
         <v>5</v>
@@ -7749,7 +6149,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
-        <v>757</v>
+        <v>292</v>
       </c>
       <c r="B113" s="11">
         <v>3</v>
@@ -7757,7 +6157,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
-        <v>758</v>
+        <v>293</v>
       </c>
       <c r="B114" s="11">
         <v>6</v>
@@ -7765,7 +6165,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
-        <v>759</v>
+        <v>294</v>
       </c>
       <c r="B115" s="11">
         <v>0</v>
@@ -7773,7 +6173,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
-        <v>760</v>
+        <v>295</v>
       </c>
       <c r="B116" s="11">
         <v>4</v>
@@ -7781,7 +6181,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
-        <v>761</v>
+        <v>296</v>
       </c>
       <c r="B117" s="11">
         <v>0</v>
@@ -7789,7 +6189,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
-        <v>762</v>
+        <v>297</v>
       </c>
       <c r="B118" s="11">
         <v>2</v>
@@ -7797,7 +6197,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
-        <v>763</v>
+        <v>298</v>
       </c>
       <c r="B119" s="11">
         <v>5</v>
@@ -7805,7 +6205,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
-        <v>764</v>
+        <v>299</v>
       </c>
       <c r="B120" s="11">
         <v>4</v>
@@ -7813,7 +6213,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
-        <v>765</v>
+        <v>300</v>
       </c>
       <c r="B121" s="11">
         <v>0</v>
@@ -7821,7 +6221,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
-        <v>766</v>
+        <v>301</v>
       </c>
       <c r="B122" s="11">
         <v>0</v>
@@ -7829,7 +6229,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
-        <v>767</v>
+        <v>302</v>
       </c>
       <c r="B123" s="11">
         <v>4</v>
@@ -7837,7 +6237,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
-        <v>768</v>
+        <v>303</v>
       </c>
       <c r="B124" s="11">
         <v>2</v>
@@ -7845,7 +6245,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="11" t="s">
-        <v>769</v>
+        <v>304</v>
       </c>
       <c r="B125" s="11">
         <v>0</v>
@@ -7853,7 +6253,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="11" t="s">
-        <v>770</v>
+        <v>305</v>
       </c>
       <c r="B126" s="11">
         <v>3</v>
@@ -7861,7 +6261,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
-        <v>771</v>
+        <v>306</v>
       </c>
       <c r="B127" s="11">
         <v>0</v>
@@ -7869,7 +6269,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="11" t="s">
-        <v>772</v>
+        <v>307</v>
       </c>
       <c r="B128" s="11">
         <v>2</v>
@@ -7877,7 +6277,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
-        <v>773</v>
+        <v>308</v>
       </c>
       <c r="B129" s="11">
         <v>0</v>
@@ -7885,7 +6285,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
-        <v>774</v>
+        <v>309</v>
       </c>
       <c r="B130" s="11">
         <v>5</v>
@@ -7893,7 +6293,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="11" t="s">
-        <v>775</v>
+        <v>310</v>
       </c>
       <c r="B131" s="11">
         <v>4</v>
@@ -7901,7 +6301,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
-        <v>776</v>
+        <v>311</v>
       </c>
       <c r="B132" s="11">
         <v>0</v>
@@ -7909,7 +6309,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="11" t="s">
-        <v>777</v>
+        <v>312</v>
       </c>
       <c r="B133" s="11">
         <v>1</v>
@@ -7917,7 +6317,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="11" t="s">
-        <v>778</v>
+        <v>313</v>
       </c>
       <c r="B134" s="11">
         <v>4</v>
@@ -7925,7 +6325,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
-        <v>779</v>
+        <v>314</v>
       </c>
       <c r="B135" s="11">
         <v>4</v>
@@ -7933,7 +6333,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="11" t="s">
-        <v>780</v>
+        <v>315</v>
       </c>
       <c r="B136" s="11">
         <v>3</v>
@@ -7941,7 +6341,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
-        <v>781</v>
+        <v>316</v>
       </c>
       <c r="B137" s="11">
         <v>0</v>
@@ -7949,7 +6349,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
-        <v>782</v>
+        <v>317</v>
       </c>
       <c r="B138" s="11">
         <v>4</v>
@@ -7957,7 +6357,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
-        <v>783</v>
+        <v>318</v>
       </c>
       <c r="B139" s="11">
         <v>3</v>
@@ -7965,7 +6365,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
-        <v>784</v>
+        <v>319</v>
       </c>
       <c r="B140" s="11">
         <v>4</v>
@@ -7973,7 +6373,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="11" t="s">
-        <v>785</v>
+        <v>320</v>
       </c>
       <c r="B141" s="11">
         <v>3</v>
@@ -7981,7 +6381,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
-        <v>786</v>
+        <v>321</v>
       </c>
       <c r="B142" s="11">
         <v>1</v>
@@ -7989,7 +6389,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
-        <v>787</v>
+        <v>322</v>
       </c>
       <c r="B143" s="11">
         <v>0</v>
@@ -7997,7 +6397,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="11" t="s">
-        <v>788</v>
+        <v>323</v>
       </c>
       <c r="B144" s="11">
         <v>0</v>
@@ -8005,7 +6405,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
-        <v>789</v>
+        <v>324</v>
       </c>
       <c r="B145" s="11">
         <v>6</v>
@@ -8013,7 +6413,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="11" t="s">
-        <v>790</v>
+        <v>325</v>
       </c>
       <c r="B146" s="11">
         <v>0</v>
@@ -8021,7 +6421,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="11" t="s">
-        <v>791</v>
+        <v>326</v>
       </c>
       <c r="B147" s="11">
         <v>2</v>
@@ -8029,7 +6429,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="11" t="s">
-        <v>792</v>
+        <v>327</v>
       </c>
       <c r="B148" s="11">
         <v>4</v>
@@ -8037,7 +6437,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="11" t="s">
-        <v>793</v>
+        <v>328</v>
       </c>
       <c r="B149" s="11">
         <v>1</v>
@@ -8045,7 +6445,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
-        <v>794</v>
+        <v>329</v>
       </c>
       <c r="B150" s="11">
         <v>0</v>
@@ -8053,7 +6453,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
-        <v>795</v>
+        <v>330</v>
       </c>
       <c r="B151" s="11">
         <v>4</v>
@@ -8061,7 +6461,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="11" t="s">
-        <v>796</v>
+        <v>331</v>
       </c>
       <c r="B152" s="11">
         <v>0</v>
@@ -8069,7 +6469,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="11" t="s">
-        <v>797</v>
+        <v>332</v>
       </c>
       <c r="B153" s="11">
         <v>3</v>
@@ -8077,7 +6477,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
-        <v>798</v>
+        <v>333</v>
       </c>
       <c r="B154" s="11">
         <v>3</v>
@@ -8085,7 +6485,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
-        <v>799</v>
+        <v>334</v>
       </c>
       <c r="B155" s="11">
         <v>0</v>
@@ -8093,7 +6493,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
-        <v>800</v>
+        <v>335</v>
       </c>
       <c r="B156" s="11">
         <v>0</v>
@@ -8101,7 +6501,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
-        <v>801</v>
+        <v>336</v>
       </c>
       <c r="B157" s="11">
         <v>3</v>
@@ -8109,7 +6509,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="11" t="s">
-        <v>802</v>
+        <v>337</v>
       </c>
       <c r="B158" s="11">
         <v>4</v>
@@ -8117,7 +6517,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="11" t="s">
-        <v>803</v>
+        <v>338</v>
       </c>
       <c r="B159" s="11">
         <v>2</v>
@@ -8125,7 +6525,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
-        <v>804</v>
+        <v>339</v>
       </c>
       <c r="B160" s="11">
         <v>3</v>
@@ -8133,7 +6533,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="11" t="s">
-        <v>805</v>
+        <v>340</v>
       </c>
       <c r="B161" s="11">
         <v>0</v>
@@ -8141,7 +6541,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="11" t="s">
-        <v>806</v>
+        <v>341</v>
       </c>
       <c r="B162" s="11">
         <v>2</v>
@@ -8149,7 +6549,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="11" t="s">
-        <v>807</v>
+        <v>342</v>
       </c>
       <c r="B163" s="11">
         <v>4</v>
@@ -8157,7 +6557,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
-        <v>808</v>
+        <v>343</v>
       </c>
       <c r="B164" s="11">
         <v>3</v>
@@ -8165,7 +6565,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="11" t="s">
-        <v>809</v>
+        <v>344</v>
       </c>
       <c r="B165" s="11">
         <v>3</v>
@@ -8173,7 +6573,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="11" t="s">
-        <v>810</v>
+        <v>345</v>
       </c>
       <c r="B166" s="11">
         <v>0</v>
@@ -8181,7 +6581,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="11" t="s">
-        <v>811</v>
+        <v>346</v>
       </c>
       <c r="B167" s="11">
         <v>4</v>
@@ -8189,7 +6589,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
-        <v>812</v>
+        <v>347</v>
       </c>
       <c r="B168" s="11">
         <v>3</v>
@@ -8197,7 +6597,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
-        <v>813</v>
+        <v>348</v>
       </c>
       <c r="B169" s="11">
         <v>6</v>
@@ -8205,7 +6605,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="11" t="s">
-        <v>814</v>
+        <v>349</v>
       </c>
       <c r="B170" s="11">
         <v>0</v>
@@ -8213,7 +6613,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="11" t="s">
-        <v>815</v>
+        <v>350</v>
       </c>
       <c r="B171" s="11">
         <v>0</v>
@@ -8221,7 +6621,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="11" t="s">
-        <v>816</v>
+        <v>351</v>
       </c>
       <c r="B172" s="11">
         <v>5</v>
@@ -8229,7 +6629,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="11" t="s">
-        <v>817</v>
+        <v>352</v>
       </c>
       <c r="B173" s="11">
         <v>3</v>
@@ -8237,7 +6637,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="11" t="s">
-        <v>818</v>
+        <v>353</v>
       </c>
       <c r="B174" s="11">
         <v>0</v>
@@ -8245,7 +6645,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="11" t="s">
-        <v>819</v>
+        <v>354</v>
       </c>
       <c r="B175" s="11">
         <v>1</v>
@@ -8253,7 +6653,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="11" t="s">
-        <v>820</v>
+        <v>355</v>
       </c>
       <c r="B176" s="11">
         <v>0</v>
@@ -8521,7 +6921,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" style="11" customWidth="1"/>
@@ -8565,7 +6965,7 @@
     </row>
     <row r="2" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>58</v>
@@ -9364,6 +7764,18 @@
         <v>1</v>
       </c>
       <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
